--- a/doc/基本設計/勤怠管理システム_設計書.xlsx
+++ b/doc/基本設計/勤怠管理システム_設計書.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
   <si>
     <t xml:space="preserve">勤怠管理システム</t>
   </si>
@@ -98,12 +98,6 @@
   </si>
   <si>
     <t xml:space="preserve">実装機能管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">認証・権限一覧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">権限管理</t>
   </si>
   <si>
     <t xml:space="preserve">■画面一覧</t>
@@ -941,9 +935,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>675360</xdr:colOff>
+      <xdr:colOff>675000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -953,7 +947,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="282960" y="1698840"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1014,9 +1008,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>675360</xdr:colOff>
+      <xdr:colOff>675000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>100440</xdr:rowOff>
+      <xdr:rowOff>100080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1026,7 +1020,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="282960" y="736560"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1087,9 +1081,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>138240</xdr:colOff>
+      <xdr:colOff>137880</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>104040</xdr:rowOff>
+      <xdr:rowOff>103680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1099,7 +1093,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2184120" y="2492640"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1160,9 +1154,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>162360</xdr:colOff>
+      <xdr:colOff>162000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>147600</xdr:rowOff>
+      <xdr:rowOff>147240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1172,7 +1166,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2208240" y="4563000"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1233,9 +1227,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>138240</xdr:colOff>
+      <xdr:colOff>137880</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>28440</xdr:rowOff>
+      <xdr:rowOff>28080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1245,7 +1239,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2184120" y="3456000"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1306,9 +1300,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>173880</xdr:colOff>
+      <xdr:colOff>173520</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1318,7 +1312,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2219760" y="5580720"/>
-          <a:ext cx="1526040" cy="578160"/>
+          <a:ext cx="1525680" cy="577800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1802,16 +1796,8 @@
       <c r="F10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1847,7 +1833,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" s="10"/>
     </row>
@@ -1856,126 +1842,126 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2003,7 +1989,7 @@
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2018,7 +2004,7 @@
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2031,7 +2017,7 @@
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2066,7 +2052,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3"/>
     </row>
@@ -2075,10 +2061,10 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>12</v>
@@ -2090,76 +2076,76 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="E9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="E10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="E11" s="8"/>
     </row>
@@ -2192,127 +2178,127 @@
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="F9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="F10" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2342,27 +2328,27 @@
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>12</v>
@@ -2370,99 +2356,99 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>12</v>
@@ -2470,79 +2456,79 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>115</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
